--- a/data/trans_orig/IP07KS_C04_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07KS_C04_2023-Habitat-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse solo/a en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según la frecuencia de sentirse solo/a, percibida por el/la menor [KIDSCREEN 10] en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,107 +720,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>918</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4502</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,94%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5013</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3,22%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>14,44%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>14,67%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6313</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>918</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4386</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1790</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6109</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>12,85%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>3167</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>965</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6946</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>10,16%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,1%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>22,28%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>3387</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5068</t>
+          <t>6961</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>5177</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1754</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9492</t>
+          <t>10566</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,93%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16751</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8243</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>24374</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>35,24%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>17,34%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>51,28%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4959</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2169</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9004</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>15,91%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>28,89%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15463</t>
+          <t>5547</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24427</t>
+          <t>10430</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>20422</t>
+          <t>22298</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11358</t>
+          <t>14328</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28888</t>
+          <t>31421</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>38,45%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>28987</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>21617</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>38011</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>60,99%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>45,48%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>79,98%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>22129</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>17690</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>26277</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>70,99%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>56,75%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>84,29%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>30959</t>
+          <t>24147</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22093</t>
+          <t>19015</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>40227</t>
+          <t>28333</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>53089</t>
+          <t>53134</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>43985</t>
+          <t>44619</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>63967</t>
+          <t>62375</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>76,34%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>47528</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>47528</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>47528</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>79194</t>
+          <t>81708</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>79194</t>
+          <t>81708</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>79194</t>
+          <t>81708</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1417</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4864</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,77%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1444</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1717</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5691</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6015</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,61%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1624</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4803</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3068</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7049</t>
+          <t>8248</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3805</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2806</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>897</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>7453</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>5,23%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>13,9%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>712</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4448</t>
+          <t>7220</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>3613</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8396</t>
+          <t>8773</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9863</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5366</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>16631</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>9,68%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5,26%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>16,32%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1416</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1704</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5027</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,64%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>6340</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,37%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>9393</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>4841</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>15738</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>9,14%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>4,71%</t>
-        </is>
-      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>10809</t>
+          <t>11567</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6085</t>
+          <t>6567</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17658</t>
+          <t>19495</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>12,25%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>34778</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>24861</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>45992</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>34,12%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>24,39%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>45,12%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>16314</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>11284</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>22531</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>30,42%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>21,04%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>42,01%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34414</t>
+          <t>17557</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25400</t>
+          <t>12115</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48116</t>
+          <t>23977</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>50728</t>
+          <t>52335</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40106</t>
+          <t>41691</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66828</t>
+          <t>66419</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>41,73%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>54976</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>44491</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>65699</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>53,94%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>43,65%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>64,46%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>31654</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>25472</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>37284</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>59,02%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>47,49%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>69,52%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>56538</t>
+          <t>33274</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43903</t>
+          <t>26739</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>66050</t>
+          <t>39442</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>88192</t>
+          <t>88251</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>75381</t>
+          <t>75384</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>100223</t>
+          <t>99223</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>62,35%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>101924</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>101924</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>101924</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>53633</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>53633</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>53633</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>102777</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>102777</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>102777</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>156410</t>
+          <t>159149</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>156410</t>
+          <t>159149</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>156410</t>
+          <t>159149</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2197,107 +2197,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>788</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3804</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3763</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>7,63%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>3734</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>788</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>4167</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2711</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7675</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4,18%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>11,84%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>2388</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>6566</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>9,1%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2565</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>678</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7032</t>
+          <t>5973</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1689</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>10978</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>19276</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>11714</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>30259</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>29,73%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>18,07%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>46,67%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>37867</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>14425</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>59419</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>52,46%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>19,98%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>82,32%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18684</t>
+          <t>14264</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11603</t>
+          <t>9384</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29277</t>
+          <t>22155</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>56551</t>
+          <t>33540</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33304</t>
+          <t>23705</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>91117</t>
+          <t>46020</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>40,32%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>42842</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>31874</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>50425</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>66,08%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>49,17%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>77,78%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>31141</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>12167</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>53142</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>43,14%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>16,86%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>73,62%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>43729</t>
+          <t>31847</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>33830</t>
+          <t>24678</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>51631</t>
+          <t>37154</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>74869</t>
+          <t>74689</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>40645</t>
+          <t>62633</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>96142</t>
+          <t>84703</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>74,2%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>64829</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>64829</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>64829</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>72183</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>72183</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>72183</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>64978</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>64978</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>64978</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>137161</t>
+          <t>114147</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137161</t>
+          <t>114147</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137161</t>
+          <t>114147</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1433</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5732</t>
+          <t>4941</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>1627</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5926</t>
+          <t>5691</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2668</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>937</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6807</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -2879,107 +2879,107 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>823</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>884</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>4374</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3808</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>8,18%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>884</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>4473</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>823</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>4353</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>4496</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>1890</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6542</t>
+          <t>10172</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4533</t>
+          <t>3330</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10031</t>
+          <t>7203</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>7396</t>
+          <t>7825</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3606</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>13911</t>
+          <t>14123</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,53%</t>
         </is>
       </c>
     </row>
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>20305</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>13913</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>27283</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>36,38%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>24,92%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>48,88%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>23111</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>17266</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>29530</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>43,21%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>32,28%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>55,21%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>20330</t>
+          <t>24645</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14346</t>
+          <t>17928</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27537</t>
+          <t>31030</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>43441</t>
+          <t>44950</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>34868</t>
+          <t>35477</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>52822</t>
+          <t>53945</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>47,87%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>29586</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>22880</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>36316</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>53,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>40,99%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>65,06%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>25090</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>18733</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>31170</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>46,91%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>35,03%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>58,28%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>30435</t>
+          <t>26379</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>23853</t>
+          <t>20079</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>37687</t>
+          <t>32747</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>55525</t>
+          <t>55965</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>46180</t>
+          <t>46178</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>64460</t>
+          <t>65043</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>57,72%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>55820</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>55820</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>55820</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>53483</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>53483</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>53483</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>56371</t>
+          <t>56865</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>56371</t>
+          <t>56865</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>56371</t>
+          <t>56865</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>109854</t>
+          <t>112685</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>109854</t>
+          <t>112685</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>109854</t>
+          <t>112685</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>903</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8818</t>
+          <t>7699</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2697</t>
+          <t>4443</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>9611</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>6653</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>3457</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>12423</t>
+          <t>14038</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>4526</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>4416</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>1428</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>9614</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>4,57%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>4717</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>9803</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2115</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>10536</t>
+          <t>11864</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -3674,72 +3674,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>18860</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>11612</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>28554</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>6,98%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>10,57%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>9835</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>5338</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>16713</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>7,94%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>18089</t>
+          <t>10768</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>11553</t>
+          <t>6098</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>27827</t>
+          <t>17063</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>27924</t>
+          <t>29628</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>19311</t>
+          <t>21226</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>38246</t>
+          <t>40997</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -3787,72 +3787,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>91110</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>73827</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>109547</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>33,73%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>27,33%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>40,56%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>82250</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>58789</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>129707</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>39,08%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>27,93%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>61,63%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>88892</t>
+          <t>62013</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>71467</t>
+          <t>51047</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>105912</t>
+          <t>75555</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>171142</t>
+          <t>153123</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>144736</t>
+          <t>131210</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>229586</t>
+          <t>172989</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -3900,72 +3900,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>156391</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>138290</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>173545</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>57,9%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>51,2%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>64,25%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>110014</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>69990</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>130953</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>52,27%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>33,25%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>62,22%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>161662</t>
+          <t>115647</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>142272</t>
+          <t>103072</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>182435</t>
+          <t>127424</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>271676</t>
+          <t>272038</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>224279</t>
+          <t>250450</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>297525</t>
+          <t>296114</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>63,31%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
